--- a/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
+++ b/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:19:44+00:00</t>
+    <t>2026-09-14T09:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -378,16 +378,26 @@
     <t>Résultats d'examens antérieurs pertinents</t>
   </si>
   <si>
-    <t>FRLMSupportingInformation.entry.historyOfPastIllness</t>
-  </si>
-  <si>
-    <t>Observation</t>
+    <t>FRLMSupportingInformation.entry.historyOfPastIllness[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCondition
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservation</t>
+  </si>
+  <si>
+    <t>Antécédents médicaux</t>
   </si>
   <si>
     <t>FRLMSupportingInformation.entry.historyOfPastProcedures</t>
   </si>
   <si>
+    <t>Antécédents chirurgicaux</t>
+  </si>
+  <si>
     <t>FRLMSupportingInformation.entry.contraIndication</t>
+  </si>
+  <si>
+    <t>Contre-indications</t>
   </si>
   <si>
     <t>FRLMSupportingInformation.entry.condition</t>
@@ -2098,10 +2108,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
@@ -2113,13 +2123,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2173,10 +2183,10 @@
         <v>118</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
@@ -2187,10 +2197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2198,10 +2208,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
@@ -2216,10 +2226,10 @@
         <v>116</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2270,13 +2280,13 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
@@ -2287,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2301,7 +2311,7 @@
         <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -2316,10 +2326,10 @@
         <v>116</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2370,13 +2380,13 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
@@ -2387,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2413,13 +2423,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2470,7 +2480,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2487,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2513,13 +2523,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2570,7 +2580,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2587,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2613,13 +2623,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2670,7 +2680,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2687,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2713,13 +2723,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2770,7 +2780,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2787,10 +2797,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2816,10 +2826,10 @@
         <v>79</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2870,7 +2880,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>

--- a/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
+++ b/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="138">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:04:12+00:00</t>
+    <t>2026-09-23T09:36:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -368,36 +368,14 @@
     <t>FRLMSection.entry</t>
   </si>
   <si>
-    <t>FRLMSupportingInformation.entry.previousResultsInformation</t>
+    <t>FRLMSupportingInformation.entry.observation</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservation
 </t>
   </si>
   <si>
-    <t>Résultats d'examens antérieurs pertinents</t>
-  </si>
-  <si>
-    <t>FRLMSupportingInformation.entry.historyOfPastIllness[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCondition
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservation</t>
-  </si>
-  <si>
-    <t>Antécédents médicaux</t>
-  </si>
-  <si>
-    <t>FRLMSupportingInformation.entry.historyOfPastProcedures</t>
-  </si>
-  <si>
-    <t>Antécédents chirurgicaux</t>
-  </si>
-  <si>
-    <t>FRLMSupportingInformation.entry.contraIndication</t>
-  </si>
-  <si>
-    <t>Contre-indications</t>
+    <t>Observation (résultat d'examen antérieur, antécédent médical ou chirurgical, contre-indication et autre observation)</t>
   </si>
   <si>
     <t>FRLMSupportingInformation.entry.condition</t>
@@ -407,7 +385,7 @@
 </t>
   </si>
   <si>
-    <t>Problème</t>
+    <t>Problème (antécédent médical, problème de santé, etc.)</t>
   </si>
   <si>
     <t>FRLMSupportingInformation.entry.device</t>
@@ -430,20 +408,40 @@
     <t>Statut grossesse</t>
   </si>
   <si>
-    <t>FRLMSupportingInformation.entry.priorMedicationAdministration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDICOMMedicationAdministration
+    <t>FRLMSupportingInformation.entry.medicationAdministration[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDICOMMedicationAdministration
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration</t>
+  </si>
+  <si>
+    <t>Produits de santé administré avant l'examen de biologie ou d'imagerie</t>
+  </si>
+  <si>
+    <t>FRLMSupportingInformation.entry.sexForClinicalUse</t>
+  </si>
+  <si>
+    <t>Sexe Clinique</t>
+  </si>
+  <si>
+    <t>FRLMSupportingInformation.entry.vaccination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMImmunisation
 </t>
   </si>
   <si>
-    <t>Produits de santé administré avant l'examen d'imagerie</t>
-  </si>
-  <si>
-    <t>FRLMSupportingInformation.entry.sexForClinicalUse</t>
-  </si>
-  <si>
-    <t>Sexe Clinique</t>
+    <t>Historique vaccinal du patient</t>
+  </si>
+  <si>
+    <t>FRLMSupportingInformation.entry.otherSupportingInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Autres informations cliniques pertinentes</t>
   </si>
 </sst>
 </file>
@@ -745,11 +743,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.50390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.50390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -779,7 +777,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="51.859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.50390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2223,13 +2221,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2297,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2311,7 +2309,7 @@
         <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -2323,13 +2321,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2380,13 +2378,13 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
@@ -2397,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2423,13 +2421,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2480,7 +2478,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2497,10 +2495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2511,7 +2509,7 @@
         <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>72</v>
@@ -2523,13 +2521,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2580,13 +2578,13 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>72</v>
@@ -2597,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2611,7 +2609,7 @@
         <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
@@ -2623,13 +2621,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2680,13 +2678,13 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
@@ -2697,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2723,13 +2721,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2780,7 +2778,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -2792,106 +2790,6 @@
         <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
+++ b/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:36:17+00:00</t>
+    <t>2026-09-28T10:07:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
+++ b/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:07:47+00:00</t>
+    <t>2026-09-30T20:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,7 +362,7 @@
     <t>FRLMSupportingInformation.entry</t>
   </si>
   <si>
-    <t>Entrées</t>
+    <t>Modèles logiques contenus dans la section</t>
   </si>
   <si>
     <t>FRLMSection.entry</t>

--- a/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
+++ b/main/ig/StructureDefinition-FRLMSupportingInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:10:21+00:00</t>
+    <t>2026-10-08T12:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
